--- a/docs/downloads/经营分_河南省区__河南西南片区_2026-10-18.xlsx
+++ b/docs/downloads/经营分_河南省区__河南西南片区_2026-10-18.xlsx
@@ -1906,34 +1906,34 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>驻马店市</t>
+          <t>南阳市</t>
         </is>
       </c>
       <c r="D16" s="3" t="inlineStr">
         <is>
-          <t>6601141847681140749</t>
+          <t>6601190165425686542</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>7天优品（驻马店天中山大道店）</t>
+          <t>7天酒店（3.0南阳西峡汽车站店）</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>7天优品(驻马店天中山大道店)</t>
+          <t>7天酒店(南阳西峡汽车站白羽南路店)</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H16" t="n">
         <v>100</v>
       </c>
       <c r="I16" t="n">
-        <v>-5</v>
+        <v>0</v>
       </c>
       <c r="J16" t="inlineStr">
         <is>
@@ -1953,13 +1953,13 @@
         <v>30</v>
       </c>
       <c r="O16" t="n">
+        <v>20</v>
+      </c>
+      <c r="P16" t="n">
+        <v>30</v>
+      </c>
+      <c r="Q16" t="n">
         <v>25</v>
-      </c>
-      <c r="P16" t="n">
-        <v>30</v>
-      </c>
-      <c r="Q16" t="n">
-        <v>20</v>
       </c>
       <c r="R16" t="n">
         <v>30</v>
@@ -1994,22 +1994,22 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>南阳市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="D17" s="3" t="inlineStr">
         <is>
-          <t>6601190165425686542</t>
+          <t>6909953315031746564</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>7天酒店（3.0南阳西峡汽车站店）</t>
+          <t>希岸酒店（平顶山和平路步行街店）</t>
         </is>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>7天酒店(南阳西峡汽车站白羽南路店)</t>
+          <t>希岸酒店(平顶山和平路步行街店)</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -2025,7 +2025,7 @@
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K17" t="n">
@@ -2041,13 +2041,13 @@
         <v>30</v>
       </c>
       <c r="O17" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P17" t="n">
         <v>30</v>
       </c>
       <c r="Q17" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="R17" t="n">
         <v>30</v>
@@ -2082,22 +2082,22 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>平顶山市</t>
+          <t>南阳市</t>
         </is>
       </c>
       <c r="D18" s="3" t="inlineStr">
         <is>
-          <t>6909953315031746564</t>
+          <t>7051413034476800035</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>希岸酒店（平顶山和平路步行街店）</t>
+          <t>维也纳酒店（南阳市政府独山大道吾悦广场店）</t>
         </is>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>希岸酒店(平顶山和平路步行街店)</t>
+          <t>维也纳酒店(5.0南阳独山大道店)</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -2113,7 +2113,7 @@
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>提质量,拿收益</t>
         </is>
       </c>
       <c r="K18" t="n">
@@ -2123,19 +2123,19 @@
         <v>10</v>
       </c>
       <c r="M18" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N18" t="n">
         <v>30</v>
       </c>
       <c r="O18" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="P18" t="n">
         <v>30</v>
       </c>
       <c r="Q18" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="R18" t="n">
         <v>30</v>
@@ -2175,22 +2175,22 @@
       </c>
       <c r="D19" s="3" t="inlineStr">
         <is>
-          <t>7051413034476800035</t>
+          <t>7024001112357210152</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>维也纳酒店（南阳市政府独山大道吾悦广场店）</t>
+          <t>维也纳酒店（南阳淅川上亿广场店）</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>维也纳酒店(5.0南阳独山大道店)</t>
+          <t>维也纳酒店(南阳淅川上亿广场店)</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H19" t="n">
@@ -2263,17 +2263,17 @@
       </c>
       <c r="D20" s="3" t="inlineStr">
         <is>
-          <t>7024001112357210152</t>
+          <t>7364262166458337291</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>维也纳酒店（南阳淅川上亿广场店）</t>
+          <t>锦江之星（南阳理工学院酒店）</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>维也纳酒店(南阳淅川上亿广场店)</t>
+          <t>锦江之星(南阳理工学院店)</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -2289,7 +2289,7 @@
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>提质量,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K20" t="n">
@@ -2299,7 +2299,7 @@
         <v>10</v>
       </c>
       <c r="M20" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N20" t="n">
         <v>30</v>
@@ -2311,7 +2311,7 @@
         <v>30</v>
       </c>
       <c r="Q20" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R20" t="n">
         <v>30</v>
@@ -2346,22 +2346,22 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>南阳市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="D21" s="3" t="inlineStr">
         <is>
-          <t>7364262166458337291</t>
+          <t>7254394547340314684</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>锦江之星（南阳理工学院酒店）</t>
+          <t>7天优品（平顶山火车站和顺路店）</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>锦江之星(南阳理工学院店)</t>
+          <t>7天优品(平顶山火车站和顺路店)</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -2370,14 +2370,14 @@
         </is>
       </c>
       <c r="H21" t="n">
-        <v>100</v>
+        <v>102</v>
       </c>
       <c r="I21" t="n">
         <v>0</v>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K21" t="n">
@@ -2387,19 +2387,19 @@
         <v>10</v>
       </c>
       <c r="M21" t="n">
-        <v>25</v>
+        <v>22</v>
       </c>
       <c r="N21" t="n">
         <v>30</v>
       </c>
       <c r="O21" t="n">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="P21" t="n">
         <v>30</v>
       </c>
       <c r="Q21" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R21" t="n">
         <v>30</v>
@@ -2434,38 +2434,38 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>平顶山市</t>
+          <t>南阳市</t>
         </is>
       </c>
       <c r="D22" s="3" t="inlineStr">
         <is>
-          <t>7254394547340314684</t>
+          <t>7036958835579291686</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>7天优品（平顶山火车站和顺路店）</t>
+          <t>7天优品Premium（南阳方城县东关店）</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>7天优品(平顶山火车站和顺路店)</t>
+          <t>7天优品Premium(南阳方城县东关店)</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H22" t="n">
-        <v>102</v>
+        <v>105</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K22" t="n">
@@ -2475,19 +2475,19 @@
         <v>10</v>
       </c>
       <c r="M22" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="N22" t="n">
         <v>30</v>
       </c>
       <c r="O22" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P22" t="n">
         <v>30</v>
       </c>
       <c r="Q22" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R22" t="n">
         <v>30</v>
@@ -2522,34 +2522,34 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>南阳市</t>
+          <t>驻马店市</t>
         </is>
       </c>
       <c r="D23" s="3" t="inlineStr">
         <is>
-          <t>7036958835579291686</t>
+          <t>6601141847681140749</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>7天优品Premium（南阳方城县东关店）</t>
+          <t>7天优品（驻马店天中山大道店）</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>7天优品Premium(南阳方城县东关店)</t>
+          <t>7天优品(驻马店天中山大道店)</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H23" t="n">
         <v>105</v>
       </c>
       <c r="I23" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J23" t="inlineStr">
         <is>
@@ -2615,33 +2615,33 @@
       </c>
       <c r="D24" s="3" t="inlineStr">
         <is>
-          <t>6601141915758888968</t>
+          <t>7098209794527332355</t>
         </is>
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（驻马店华源学府店）</t>
+          <t>维也纳国际酒店（驻马店建苑店）</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(驻马店华源学府店)</t>
+          <t>维也纳国际酒店(建苑店)</t>
         </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H24" t="n">
         <v>105</v>
       </c>
       <c r="I24" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J24" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K24" t="n">
@@ -2651,7 +2651,7 @@
         <v>10</v>
       </c>
       <c r="M24" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N24" t="n">
         <v>30</v>
@@ -2663,7 +2663,7 @@
         <v>30</v>
       </c>
       <c r="Q24" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="R24" t="n">
         <v>30</v>
@@ -2698,22 +2698,22 @@
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>驻马店市</t>
+          <t>南阳市</t>
         </is>
       </c>
       <c r="D25" s="3" t="inlineStr">
         <is>
-          <t>7098209794527332355</t>
+          <t>7414729323095001100</t>
         </is>
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（驻马店建苑店）</t>
+          <t>锦江之星（南阳社旗赊店古镇酒店）</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(建苑店)</t>
+          <t>锦江之星(南阳社旗赊店古镇酒店)</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
@@ -2725,11 +2725,11 @@
         <v>105</v>
       </c>
       <c r="I25" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,提质量</t>
         </is>
       </c>
       <c r="K25" t="n">
@@ -2739,19 +2739,19 @@
         <v>10</v>
       </c>
       <c r="M25" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="N25" t="n">
         <v>30</v>
       </c>
       <c r="O25" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="P25" t="n">
         <v>30</v>
       </c>
       <c r="Q25" t="n">
-        <v>15</v>
+        <v>30</v>
       </c>
       <c r="R25" t="n">
         <v>30</v>
@@ -2786,38 +2786,38 @@
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>南阳市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="D26" s="3" t="inlineStr">
         <is>
-          <t>7414729323095001100</t>
+          <t>7549011545234425908</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>锦江之星（南阳社旗赊店古镇酒店）</t>
+          <t>锦江之星（平顶山舞钢石漫滩大道店）</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>锦江之星(南阳社旗赊店古镇酒店)</t>
+          <t>锦江之星(平顶山舞钢石漫滩大道店)</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H26" t="n">
         <v>105</v>
       </c>
       <c r="I26" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>稳房源,提质量</t>
+          <t>稳房源,提质量,拿收益</t>
         </is>
       </c>
       <c r="K26" t="n">
@@ -2827,7 +2827,7 @@
         <v>10</v>
       </c>
       <c r="M26" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="N26" t="n">
         <v>30</v>
@@ -2839,7 +2839,7 @@
         <v>30</v>
       </c>
       <c r="Q26" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="R26" t="n">
         <v>30</v>
@@ -2879,33 +2879,33 @@
       </c>
       <c r="D27" s="3" t="inlineStr">
         <is>
-          <t>7549011545234425908</t>
+          <t>7507506953703950363</t>
         </is>
       </c>
       <c r="E27" t="inlineStr">
         <is>
-          <t>锦江之星（平顶山舞钢石漫滩大道店）</t>
+          <t>麗枫酒店（平顶山万达广场店）</t>
         </is>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>锦江之星(平顶山舞钢石漫滩大道店)</t>
+          <t>麗枫酒店(平顶山万达广场店)</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H27" t="n">
         <v>105</v>
       </c>
       <c r="I27" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J27" t="inlineStr">
         <is>
-          <t>稳房源,提质量,拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K27" t="n">
@@ -2921,13 +2921,13 @@
         <v>30</v>
       </c>
       <c r="O27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="P27" t="n">
         <v>30</v>
       </c>
       <c r="Q27" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R27" t="n">
         <v>30</v>
@@ -2962,22 +2962,22 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>平顶山市</t>
+          <t>南阳市</t>
         </is>
       </c>
       <c r="D28" s="3" t="inlineStr">
         <is>
-          <t>7507506953703950363</t>
+          <t>7391328266314844214</t>
         </is>
       </c>
       <c r="E28" t="inlineStr">
         <is>
-          <t>麗枫酒店（平顶山万达广场店）</t>
+          <t>IU酒店（南阳师范学院卧龙岗景区店）</t>
         </is>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>麗枫酒店(平顶山万达广场店)</t>
+          <t>IU酒店4.0(南阳师范学院卧龙岗景区店)</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
@@ -2986,7 +2986,7 @@
         </is>
       </c>
       <c r="H28" t="n">
-        <v>105</v>
+        <v>110</v>
       </c>
       <c r="I28" t="n">
         <v>0</v>
@@ -3015,7 +3015,7 @@
         <v>30</v>
       </c>
       <c r="Q28" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R28" t="n">
         <v>30</v>
@@ -3050,22 +3050,22 @@
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>南阳市</t>
+          <t>驻马店市</t>
         </is>
       </c>
       <c r="D29" s="3" t="inlineStr">
         <is>
-          <t>7391328266314844214</t>
+          <t>7373510268553857034</t>
         </is>
       </c>
       <c r="E29" t="inlineStr">
         <is>
-          <t>IU酒店（南阳师范学院卧龙岗景区店）</t>
+          <t>维也纳3好酒店（驻马店遂平金博大广场店）</t>
         </is>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>IU酒店4.0(南阳师范学院卧龙岗景区店)</t>
+          <t>维也纳3好酒店(遂平金博大商业广场店)</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
@@ -3077,11 +3077,11 @@
         <v>110</v>
       </c>
       <c r="I29" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J29" t="inlineStr">
         <is>
-          <t>稳房源,拿收益</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K29" t="n">
@@ -3091,7 +3091,7 @@
         <v>10</v>
       </c>
       <c r="M29" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N29" t="n">
         <v>30</v>
@@ -3103,7 +3103,7 @@
         <v>30</v>
       </c>
       <c r="Q29" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="R29" t="n">
         <v>30</v>
@@ -3143,17 +3143,17 @@
       </c>
       <c r="D30" s="3" t="inlineStr">
         <is>
-          <t>7373510268553857034</t>
+          <t>6601141915758888968</t>
         </is>
       </c>
       <c r="E30" t="inlineStr">
         <is>
-          <t>维也纳3好酒店（驻马店遂平金博大广场店）</t>
+          <t>维也纳国际酒店（驻马店华源学府店）</t>
         </is>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>维也纳3好酒店(遂平金博大商业广场店)</t>
+          <t>维也纳国际酒店(驻马店华源学府店)</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
@@ -3169,7 +3169,7 @@
       </c>
       <c r="J30" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源,拿收益</t>
         </is>
       </c>
       <c r="K30" t="n">
@@ -3179,7 +3179,7 @@
         <v>10</v>
       </c>
       <c r="M30" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N30" t="n">
         <v>30</v>
@@ -3191,7 +3191,7 @@
         <v>30</v>
       </c>
       <c r="Q30" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="R30" t="n">
         <v>30</v>
@@ -3246,7 +3246,7 @@
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H31" t="n">
@@ -3490,38 +3490,38 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>南阳市</t>
+          <t>平顶山市</t>
         </is>
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>7039862551710009378</t>
+          <t>7553874749995911214</t>
         </is>
       </c>
       <c r="E34" t="inlineStr">
         <is>
-          <t>维也纳国际酒店（5.0版南阳邓州迎宾馆店）</t>
+          <t>锦江之星（平顶山汝州中央公园店）</t>
         </is>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>维也纳国际酒店(河南邓州迎宾馆店)</t>
+          <t>锦江之星酒店(汝州中央公园店)</t>
         </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
-          <t>未认证</t>
+          <t>已认证</t>
         </is>
       </c>
       <c r="H34" t="n">
-        <v>115</v>
+        <v>110</v>
       </c>
       <c r="I34" t="n">
-        <v>0</v>
+        <v>-5</v>
       </c>
       <c r="J34" t="inlineStr">
         <is>
-          <t>稳房源</t>
+          <t>拿收益</t>
         </is>
       </c>
       <c r="K34" t="n">
@@ -3531,7 +3531,7 @@
         <v>10</v>
       </c>
       <c r="M34" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="N34" t="n">
         <v>30</v>
@@ -3543,7 +3543,7 @@
         <v>30</v>
       </c>
       <c r="Q34" t="n">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="R34" t="n">
         <v>30</v>
@@ -3578,38 +3578,38 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>平顶山市</t>
+          <t>南阳市</t>
         </is>
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>7512278663983794213</t>
+          <t>7039862551710009378</t>
         </is>
       </c>
       <c r="E35" t="inlineStr">
         <is>
-          <t>维也纳酒店（5.0深化版平顶山卫东区万达广场店）</t>
+          <t>维也纳国际酒店（5.0版南阳邓州迎宾馆店）</t>
         </is>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>维也纳酒店(平顶山万达广场店)</t>
+          <t>维也纳国际酒店(河南邓州迎宾馆店)</t>
         </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
-          <t>已认证</t>
+          <t>未认证</t>
         </is>
       </c>
       <c r="H35" t="n">
         <v>115</v>
       </c>
       <c r="I35" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="J35" t="inlineStr">
         <is>
-          <t>拿收益</t>
+          <t>稳房源</t>
         </is>
       </c>
       <c r="K35" t="n">
@@ -3619,7 +3619,7 @@
         <v>10</v>
       </c>
       <c r="M35" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="N35" t="n">
         <v>30</v>
@@ -3631,7 +3631,7 @@
         <v>30</v>
       </c>
       <c r="Q35" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="R35" t="n">
         <v>30</v>
@@ -3671,17 +3671,17 @@
       </c>
       <c r="D36" s="3" t="inlineStr">
         <is>
-          <t>7553874749995911214</t>
+          <t>7512278663983794213</t>
         </is>
       </c>
       <c r="E36" t="inlineStr">
         <is>
-          <t>锦江之星（平顶山汝州中央公园店）</t>
+          <t>维也纳酒店（5.0深化版平顶山卫东区万达广场店）</t>
         </is>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>锦江之星酒店(汝州中央公园店)</t>
+          <t>维也纳酒店(平顶山万达广场店)</t>
         </is>
       </c>
       <c r="G36" t="inlineStr">
@@ -3693,7 +3693,7 @@
         <v>115</v>
       </c>
       <c r="I36" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="J36" t="inlineStr">
         <is>
